--- a/Macro Inv Tarde/VALORIZADO FALTANTES IMPO.xlsx
+++ b/Macro Inv Tarde/VALORIZADO FALTANTES IMPO.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="130">
   <si>
     <t>Categoría</t>
   </si>
@@ -61,6 +61,9 @@
     <t>7059</t>
   </si>
   <si>
+    <t>7086</t>
+  </si>
+  <si>
     <t>235383</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>1824680C1</t>
   </si>
   <si>
+    <t>1S5-164/21128983</t>
+  </si>
+  <si>
     <t>20382B</t>
   </si>
   <si>
@@ -79,15 +85,9 @@
     <t>3202C9129</t>
   </si>
   <si>
-    <t>363-4009/1613</t>
-  </si>
-  <si>
     <t>4302712/8398</t>
   </si>
   <si>
-    <t>7215/07</t>
-  </si>
-  <si>
     <t>9501/9471 2TOR</t>
   </si>
   <si>
@@ -103,12 +103,12 @@
     <t>R230072 EUCLID</t>
   </si>
   <si>
-    <t>VAD25 09 10</t>
-  </si>
-  <si>
     <t>WAB9700519502</t>
   </si>
   <si>
+    <t>X007785/ECL1942/SC</t>
+  </si>
+  <si>
     <t>X8870342</t>
   </si>
   <si>
@@ -151,6 +151,9 @@
     <t>A7331</t>
   </si>
   <si>
+    <t>3278W335/43067</t>
+  </si>
+  <si>
     <t>1229K3001</t>
   </si>
   <si>
@@ -163,10 +166,10 @@
     <t>14897</t>
   </si>
   <si>
-    <t>286171R</t>
-  </si>
-  <si>
-    <t>4303796/4301527WAP</t>
+    <t>17515</t>
+  </si>
+  <si>
+    <t>126180WAP</t>
   </si>
   <si>
     <t>56929/500.946</t>
@@ -193,27 +196,27 @@
     <t>INTERNATIONAL</t>
   </si>
   <si>
+    <t>GOODYEAR</t>
+  </si>
+  <si>
     <t>GTD</t>
   </si>
   <si>
     <t>MERITOR</t>
   </si>
   <si>
-    <t>STEMCO</t>
-  </si>
-  <si>
     <t>MAHLE</t>
   </si>
   <si>
     <t>EUCLID</t>
   </si>
   <si>
-    <t>VADEN</t>
-  </si>
-  <si>
     <t>WABCO</t>
   </si>
   <si>
+    <t>TORCTITE</t>
+  </si>
+  <si>
     <t>EATON CLUTCH</t>
   </si>
   <si>
@@ -226,7 +229,7 @@
     <t>ELGIN</t>
   </si>
   <si>
-    <t>BENDIX</t>
+    <t>DAYCO</t>
   </si>
   <si>
     <t>WAP</t>
@@ -244,6 +247,9 @@
     <t>BOLSA SILLA CZ TODAS INTER</t>
   </si>
   <si>
+    <t>BOLSA SILLA CARE PANELA KW 2005...</t>
+  </si>
+  <si>
     <t>PISTA AXIAL EJE DE TOMA FS4205A</t>
   </si>
   <si>
@@ -253,6 +259,9 @@
     <t>ROTOR TODAS LAS VALVULAS DT466 ELECTRONI</t>
   </si>
   <si>
+    <t>BOLSA SUSPENSION CABINA MACK VISION</t>
+  </si>
+  <si>
     <t>PIÑÓN 2DA TREN FIJO 14715/16915</t>
   </si>
   <si>
@@ -262,15 +271,9 @@
     <t>EJE LATERAL TRAS 46160 ANTIPATINAJE RECT</t>
   </si>
   <si>
-    <t>TAPA NEGRA DEFENDER  PASTA 5 1/2" GRANDE</t>
-  </si>
-  <si>
     <t>RODILLO TREN FIJO PARTE TRAS - TODAS 18</t>
   </si>
   <si>
-    <t>BOLSA SUSPENSION CABINA FREIGTHLINER</t>
-  </si>
-  <si>
     <t>BOLSA TAN10.12ANx5.87CCx24.50AL+7.88D+2T</t>
   </si>
   <si>
@@ -286,12 +289,12 @@
     <t>TERMINAL 2090 IZQUIERDA EUCLID</t>
   </si>
   <si>
-    <t>CULATA COMPLETA BUS RUNNER MOTOR ISL2,</t>
-  </si>
-  <si>
     <t>EMPAQUETADURA SERVO EMBRAGUE RUNNER</t>
   </si>
   <si>
+    <t>ABRAZADERA EXOSTO 5"</t>
+  </si>
+  <si>
     <t>HINO PIN MONO REDUCTOR</t>
   </si>
   <si>
@@ -334,6 +337,9 @@
     <t>PATA SINCRONIZADOR K-3492</t>
   </si>
   <si>
+    <t>CRUCETA ESCUALIZACION 46160</t>
+  </si>
+  <si>
     <t>ARANDELA SATELITE ESCUALIZACION 46160</t>
   </si>
   <si>
@@ -346,10 +352,10 @@
     <t>RESORTE</t>
   </si>
   <si>
-    <t>VALVULA DE FRENO E-6 PARA CHEVROLET Y BRIGADIER (REMANUFACTURADA COLOR AZUL)</t>
-  </si>
-  <si>
-    <t>PIÑON DE 4TA EJE CORREDIZO 4205</t>
+    <t>CORREA PARA COLUMBIA SERIE60 12LT</t>
+  </si>
+  <si>
+    <t>ARANDELA SATELITE DIVISOR 46 LBS PLANA</t>
   </si>
   <si>
     <t>TEFLON SUSPENSIÓN HOJA ZETA</t>
@@ -370,7 +376,7 @@
     <t>USA</t>
   </si>
   <si>
-    <t>WAP/TRANSMISION</t>
+    <t>WAP/DIFERENCIAL-CARDAN</t>
   </si>
   <si>
     <t>Unidad</t>
@@ -391,13 +397,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/10/2025 09:44:16</t>
+    <t>Período: 30/11/2025 13:41:04</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 23/10/2025 09:52:47</t>
+    <t>Fecha y hora de generación: 05/11/2025 13:41:37</t>
   </si>
 </sst>
 </file>
@@ -811,28 +817,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -848,7 +854,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -864,12 +870,12 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="I7" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -921,19 +927,19 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -956,7 +962,7 @@
         <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
         <v>56</v>
@@ -965,16 +971,16 @@
         <v>56</v>
       </c>
       <c r="I11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>27548.37</v>
+        <v>140713.63</v>
       </c>
       <c r="L11">
-        <v>55096.74</v>
+        <v>140713.63</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -988,7 +994,7 @@
         <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
         <v>57</v>
@@ -997,16 +1003,16 @@
         <v>57</v>
       </c>
       <c r="I12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J12">
         <v>2</v>
       </c>
       <c r="K12">
-        <v>287070.62</v>
+        <v>27548.37</v>
       </c>
       <c r="L12">
-        <v>574141.24</v>
+        <v>55096.74</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1020,7 +1026,7 @@
         <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
         <v>58</v>
@@ -1029,16 +1035,16 @@
         <v>58</v>
       </c>
       <c r="I13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J13">
         <v>2</v>
       </c>
       <c r="K13">
-        <v>20866.91</v>
+        <v>287070.62</v>
       </c>
       <c r="L13">
-        <v>41733.82</v>
+        <v>574141.24</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1049,28 +1055,28 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J14">
         <v>2</v>
       </c>
       <c r="K14">
-        <v>177348.88</v>
+        <v>20866.91</v>
       </c>
       <c r="L14">
-        <v>354697.76</v>
+        <v>41733.82</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1081,28 +1087,28 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>70851.95</v>
+        <v>69586.60000000001</v>
       </c>
       <c r="L15">
-        <v>283407.8</v>
+        <v>347933</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1113,28 +1119,28 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I16" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J16">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K16">
-        <v>525495.8</v>
+        <v>177348.88</v>
       </c>
       <c r="L16">
-        <v>6305949.6</v>
+        <v>354697.76</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1148,7 +1154,7 @@
         <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
         <v>61</v>
@@ -1157,16 +1163,16 @@
         <v>61</v>
       </c>
       <c r="I17" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>41542.9</v>
+        <v>70360.37</v>
       </c>
       <c r="L17">
-        <v>83085.8</v>
+        <v>492522.59</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1177,28 +1183,28 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="I18" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K18">
-        <v>52431.62</v>
+        <v>525495.8</v>
       </c>
       <c r="L18">
-        <v>209726.48</v>
+        <v>6305949.6</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1209,28 +1215,28 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K19">
-        <v>91384.38</v>
+        <v>52431.62</v>
       </c>
       <c r="L19">
-        <v>182768.76</v>
+        <v>209726.48</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1241,19 +1247,19 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I20" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1273,19 +1279,19 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F21" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I21" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J21">
         <v>2</v>
@@ -1305,19 +1311,19 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I22" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1337,19 +1343,19 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I23" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J23">
         <v>20</v>
@@ -1369,19 +1375,19 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E24" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F24" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I24" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -1401,28 +1407,28 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I25" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J25">
         <v>1</v>
       </c>
       <c r="K25">
-        <v>348949.42</v>
+        <v>150117.48</v>
       </c>
       <c r="L25">
-        <v>348949.42</v>
+        <v>150117.48</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1433,28 +1439,28 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I26" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="K26">
-        <v>150117.48</v>
+        <v>25537.92</v>
       </c>
       <c r="L26">
-        <v>150117.48</v>
+        <v>25537.92</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1465,19 +1471,19 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I27" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J27">
         <v>5</v>
@@ -1497,19 +1503,19 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J28">
         <v>2</v>
@@ -1529,19 +1535,19 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I29" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J29">
         <v>47</v>
@@ -1561,19 +1567,19 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I30" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J30">
         <v>3</v>
@@ -1593,19 +1599,19 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D31" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I31" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -1625,19 +1631,19 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E32" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F32" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -1657,19 +1663,19 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F33" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -1689,19 +1695,19 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I34" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -1721,28 +1727,28 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I35" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J35">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="K35">
         <v>18048.24</v>
       </c>
       <c r="L35">
-        <v>14185916.64</v>
+        <v>14294206.08</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -1753,19 +1759,19 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D36" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E36" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F36" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I36" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J36">
         <v>60</v>
@@ -1785,19 +1791,19 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D37" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E37" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F37" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I37" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J37">
         <v>13</v>
@@ -1817,19 +1823,19 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D38" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E38" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F38" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I38" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -1849,19 +1855,19 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E39" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F39" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I39" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -1881,19 +1887,19 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D40" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I40" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J40">
         <v>19</v>
@@ -1913,92 +1919,92 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D41" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E41" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F41" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I41" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J41">
-        <v>360</v>
+        <v>1</v>
       </c>
       <c r="K41">
-        <v>3512.14</v>
+        <v>114045.11</v>
       </c>
       <c r="L41">
-        <v>1264370.4</v>
+        <v>114045.11</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E42" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F42" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I42" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J42">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="K42">
-        <v>12659.05</v>
+        <v>3512.14</v>
       </c>
       <c r="L42">
-        <v>4607894.2</v>
+        <v>1264370.4</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B43" t="s">
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E43" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F43" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="I43" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J43">
-        <v>8</v>
+        <v>364</v>
       </c>
       <c r="K43">
-        <v>229850.62</v>
+        <v>12659.05</v>
       </c>
       <c r="L43">
-        <v>1838804.96</v>
+        <v>4607894.2</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2009,28 +2015,28 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D44" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E44" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F44" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I44" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J44">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="K44">
-        <v>663.89</v>
+        <v>229850.62</v>
       </c>
       <c r="L44">
-        <v>39833.4</v>
+        <v>1838804.96</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2041,28 +2047,28 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D45" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E45" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F45" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="I45" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J45">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="K45">
-        <v>209975.56</v>
+        <v>663.89</v>
       </c>
       <c r="L45">
-        <v>209975.56</v>
+        <v>39833.4</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2076,25 +2082,25 @@
         <v>71</v>
       </c>
       <c r="D46" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E46" t="s">
         <v>71</v>
       </c>
       <c r="F46" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="I46" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J46">
         <v>1</v>
       </c>
       <c r="K46">
-        <v>163002.7</v>
+        <v>12173.17</v>
       </c>
       <c r="L46">
-        <v>163002.7</v>
+        <v>12173.17</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2108,25 +2114,25 @@
         <v>72</v>
       </c>
       <c r="D47" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E47" t="s">
         <v>72</v>
       </c>
       <c r="F47" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="I47" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K47">
-        <v>15384.67</v>
+        <v>9156.48</v>
       </c>
       <c r="L47">
-        <v>15384.67</v>
+        <v>36625.92</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2140,7 +2146,7 @@
         <v>73</v>
       </c>
       <c r="D48" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E48" t="s">
         <v>73</v>
@@ -2149,16 +2155,16 @@
         <v>73</v>
       </c>
       <c r="I48" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K48">
-        <v>193066.84</v>
+        <v>15384.67</v>
       </c>
       <c r="L48">
-        <v>386133.68</v>
+        <v>15384.67</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2169,28 +2175,28 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D49" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E49" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F49" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I49" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J49">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K49">
-        <v>26517.61</v>
+        <v>193066.84</v>
       </c>
       <c r="L49">
-        <v>132588.05</v>
+        <v>386133.68</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2204,24 +2210,56 @@
         <v>74</v>
       </c>
       <c r="D50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E50" t="s">
+        <v>74</v>
+      </c>
+      <c r="F50" t="s">
+        <v>74</v>
+      </c>
+      <c r="I50" t="s">
+        <v>121</v>
+      </c>
+      <c r="J50">
+        <v>5</v>
+      </c>
+      <c r="K50">
+        <v>26517.61</v>
+      </c>
+      <c r="L50">
+        <v>132588.05</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51" t="s">
         <v>117</v>
       </c>
-      <c r="F50" t="s">
-        <v>117</v>
-      </c>
-      <c r="I50" t="s">
+      <c r="E51" t="s">
         <v>119</v>
       </c>
-      <c r="J50">
+      <c r="F51" t="s">
+        <v>119</v>
+      </c>
+      <c r="I51" t="s">
+        <v>121</v>
+      </c>
+      <c r="J51">
         <v>1</v>
       </c>
-      <c r="K50">
+      <c r="K51">
         <v>39099.54</v>
       </c>
-      <c r="L50">
+      <c r="L51">
         <v>39099.54</v>
       </c>
     </row>

--- a/Macro Inv Tarde/VALORIZADO FALTANTES IMPO.xlsx
+++ b/Macro Inv Tarde/VALORIZADO FALTANTES IMPO.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="133">
   <si>
     <t>Categoría</t>
   </si>
@@ -61,6 +61,9 @@
     <t>7059</t>
   </si>
   <si>
+    <t>7086</t>
+  </si>
+  <si>
     <t>235383</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>1824680C1</t>
   </si>
   <si>
+    <t>1S5-164/21128983</t>
+  </si>
+  <si>
     <t>20382B</t>
   </si>
   <si>
@@ -79,15 +85,9 @@
     <t>3202C9129</t>
   </si>
   <si>
-    <t>363-4009/1613</t>
-  </si>
-  <si>
     <t>4302712/8398</t>
   </si>
   <si>
-    <t>7215/07</t>
-  </si>
-  <si>
     <t>9501/9471 2TOR</t>
   </si>
   <si>
@@ -103,12 +103,12 @@
     <t>R230072 EUCLID</t>
   </si>
   <si>
-    <t>VAD25 09 10</t>
-  </si>
-  <si>
     <t>WAB9700519502</t>
   </si>
   <si>
+    <t>X007785/ECL1942/SC</t>
+  </si>
+  <si>
     <t>X8870342</t>
   </si>
   <si>
@@ -151,6 +151,9 @@
     <t>A7331</t>
   </si>
   <si>
+    <t>3278W335/43067</t>
+  </si>
+  <si>
     <t>1229K3001</t>
   </si>
   <si>
@@ -163,12 +166,15 @@
     <t>14897</t>
   </si>
   <si>
-    <t>286171R</t>
+    <t>17515</t>
   </si>
   <si>
     <t>4303796/4301527WAP</t>
   </si>
   <si>
+    <t>126180WAP</t>
+  </si>
+  <si>
     <t>56929/500.946</t>
   </si>
   <si>
@@ -193,27 +199,27 @@
     <t>INTERNATIONAL</t>
   </si>
   <si>
+    <t>GOODYEAR</t>
+  </si>
+  <si>
     <t>GTD</t>
   </si>
   <si>
     <t>MERITOR</t>
   </si>
   <si>
-    <t>STEMCO</t>
-  </si>
-  <si>
     <t>MAHLE</t>
   </si>
   <si>
     <t>EUCLID</t>
   </si>
   <si>
-    <t>VADEN</t>
-  </si>
-  <si>
     <t>WABCO</t>
   </si>
   <si>
+    <t>TORCTITE</t>
+  </si>
+  <si>
     <t>EATON CLUTCH</t>
   </si>
   <si>
@@ -226,7 +232,7 @@
     <t>ELGIN</t>
   </si>
   <si>
-    <t>BENDIX</t>
+    <t>DAYCO</t>
   </si>
   <si>
     <t>WAP</t>
@@ -244,6 +250,9 @@
     <t>BOLSA SILLA CZ TODAS INTER</t>
   </si>
   <si>
+    <t>BOLSA SILLA CARE PANELA KW 2005...</t>
+  </si>
+  <si>
     <t>PISTA AXIAL EJE DE TOMA FS4205A</t>
   </si>
   <si>
@@ -253,6 +262,9 @@
     <t>ROTOR TODAS LAS VALVULAS DT466 ELECTRONI</t>
   </si>
   <si>
+    <t>BOLSA SUSPENSION CABINA MACK VISION</t>
+  </si>
+  <si>
     <t>PIÑÓN 2DA TREN FIJO 14715/16915</t>
   </si>
   <si>
@@ -262,15 +274,9 @@
     <t>EJE LATERAL TRAS 46160 ANTIPATINAJE RECT</t>
   </si>
   <si>
-    <t>TAPA NEGRA DEFENDER  PASTA 5 1/2" GRANDE</t>
-  </si>
-  <si>
     <t>RODILLO TREN FIJO PARTE TRAS - TODAS 18</t>
   </si>
   <si>
-    <t>BOLSA SUSPENSION CABINA FREIGTHLINER</t>
-  </si>
-  <si>
     <t>BOLSA TAN10.12ANx5.87CCx24.50AL+7.88D+2T</t>
   </si>
   <si>
@@ -286,12 +292,12 @@
     <t>TERMINAL 2090 IZQUIERDA EUCLID</t>
   </si>
   <si>
-    <t>CULATA COMPLETA BUS RUNNER MOTOR ISL2,</t>
-  </si>
-  <si>
     <t>EMPAQUETADURA SERVO EMBRAGUE RUNNER</t>
   </si>
   <si>
+    <t>ABRAZADERA EXOSTO 5"</t>
+  </si>
+  <si>
     <t>HINO PIN MONO REDUCTOR</t>
   </si>
   <si>
@@ -334,6 +340,9 @@
     <t>PATA SINCRONIZADOR K-3492</t>
   </si>
   <si>
+    <t>CRUCETA ESCUALIZACION 46160</t>
+  </si>
+  <si>
     <t>ARANDELA SATELITE ESCUALIZACION 46160</t>
   </si>
   <si>
@@ -346,12 +355,15 @@
     <t>RESORTE</t>
   </si>
   <si>
-    <t>VALVULA DE FRENO E-6 PARA CHEVROLET Y BRIGADIER (REMANUFACTURADA COLOR AZUL)</t>
+    <t>CORREA PARA COLUMBIA SERIE60 12LT</t>
   </si>
   <si>
     <t>PIÑON DE 4TA EJE CORREDIZO 4205</t>
   </si>
   <si>
+    <t>ARANDELA SATELITE DIVISOR 46 LBS PLANA</t>
+  </si>
+  <si>
     <t>TEFLON SUSPENSIÓN HOJA ZETA</t>
   </si>
   <si>
@@ -373,6 +385,9 @@
     <t>WAP/TRANSMISION</t>
   </si>
   <si>
+    <t>WAP/DIFERENCIAL-CARDAN</t>
+  </si>
+  <si>
     <t>Unidad</t>
   </si>
   <si>
@@ -391,13 +406,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/10/2025 09:44:16</t>
+    <t>Período: 30/11/2025 12:35:17</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 23/10/2025 09:52:47</t>
+    <t>Fecha y hora de generación: 04/11/2025 12:35:43</t>
   </si>
 </sst>
 </file>
@@ -811,28 +826,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -848,7 +863,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -864,12 +879,12 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="I7" s="5" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -921,19 +936,19 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F10" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I10" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -953,28 +968,28 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I11" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>27548.37</v>
+        <v>140713.63</v>
       </c>
       <c r="L11">
-        <v>55096.74</v>
+        <v>140713.63</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -985,28 +1000,28 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I12" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J12">
         <v>2</v>
       </c>
       <c r="K12">
-        <v>287070.62</v>
+        <v>27548.37</v>
       </c>
       <c r="L12">
-        <v>574141.24</v>
+        <v>55096.74</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1017,28 +1032,28 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I13" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J13">
         <v>2</v>
       </c>
       <c r="K13">
-        <v>20866.91</v>
+        <v>287070.62</v>
       </c>
       <c r="L13">
-        <v>41733.82</v>
+        <v>574141.24</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1049,28 +1064,28 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I14" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J14">
         <v>2</v>
       </c>
       <c r="K14">
-        <v>177348.88</v>
+        <v>20866.91</v>
       </c>
       <c r="L14">
-        <v>354697.76</v>
+        <v>41733.82</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1081,28 +1096,28 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I15" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>70851.95</v>
+        <v>69586.60000000001</v>
       </c>
       <c r="L15">
-        <v>283407.8</v>
+        <v>347933</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1113,28 +1128,28 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I16" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J16">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K16">
-        <v>525495.8</v>
+        <v>177348.88</v>
       </c>
       <c r="L16">
-        <v>6305949.6</v>
+        <v>354697.76</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1145,28 +1160,28 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I17" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>41542.9</v>
+        <v>70360.37</v>
       </c>
       <c r="L17">
-        <v>83085.8</v>
+        <v>492522.59</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1177,28 +1192,28 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I18" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K18">
-        <v>52431.62</v>
+        <v>525495.8</v>
       </c>
       <c r="L18">
-        <v>209726.48</v>
+        <v>6305949.6</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1209,28 +1224,28 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I19" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K19">
-        <v>91384.38</v>
+        <v>52431.62</v>
       </c>
       <c r="L19">
-        <v>182768.76</v>
+        <v>209726.48</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1241,19 +1256,19 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I20" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1273,19 +1288,19 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E21" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F21" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I21" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J21">
         <v>2</v>
@@ -1305,19 +1320,19 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E22" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I22" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1337,19 +1352,19 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I23" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J23">
         <v>20</v>
@@ -1369,19 +1384,19 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E24" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F24" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I24" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -1401,28 +1416,28 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I25" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J25">
         <v>1</v>
       </c>
       <c r="K25">
-        <v>348949.42</v>
+        <v>150117.48</v>
       </c>
       <c r="L25">
-        <v>348949.42</v>
+        <v>150117.48</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1433,28 +1448,28 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E26" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F26" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I26" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="K26">
-        <v>150117.48</v>
+        <v>25537.92</v>
       </c>
       <c r="L26">
-        <v>150117.48</v>
+        <v>25537.92</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1465,19 +1480,19 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I27" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J27">
         <v>5</v>
@@ -1497,19 +1512,19 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I28" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J28">
         <v>2</v>
@@ -1529,19 +1544,19 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E29" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F29" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I29" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J29">
         <v>47</v>
@@ -1561,19 +1576,19 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F30" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I30" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J30">
         <v>3</v>
@@ -1593,19 +1608,19 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D31" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E31" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I31" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -1625,19 +1640,19 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D32" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E32" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F32" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I32" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -1657,19 +1672,19 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E33" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F33" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I33" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -1689,19 +1704,19 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D34" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E34" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F34" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I34" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -1721,28 +1736,28 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D35" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E35" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F35" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I35" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J35">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="K35">
         <v>18048.24</v>
       </c>
       <c r="L35">
-        <v>14185916.64</v>
+        <v>14294206.08</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -1753,19 +1768,19 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D36" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E36" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F36" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I36" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J36">
         <v>60</v>
@@ -1785,19 +1800,19 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D37" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E37" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F37" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I37" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J37">
         <v>13</v>
@@ -1817,19 +1832,19 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D38" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E38" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F38" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I38" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -1849,19 +1864,19 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D39" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E39" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F39" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I39" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -1881,19 +1896,19 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D40" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E40" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F40" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I40" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J40">
         <v>19</v>
@@ -1913,92 +1928,92 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D41" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E41" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F41" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I41" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J41">
-        <v>360</v>
+        <v>1</v>
       </c>
       <c r="K41">
-        <v>3512.14</v>
+        <v>114045.11</v>
       </c>
       <c r="L41">
-        <v>1264370.4</v>
+        <v>114045.11</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E42" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F42" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I42" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J42">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="K42">
-        <v>12659.05</v>
+        <v>3512.14</v>
       </c>
       <c r="L42">
-        <v>4607894.2</v>
+        <v>1264370.4</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B43" t="s">
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D43" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E43" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F43" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I43" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J43">
-        <v>8</v>
+        <v>364</v>
       </c>
       <c r="K43">
-        <v>229850.62</v>
+        <v>12659.05</v>
       </c>
       <c r="L43">
-        <v>1838804.96</v>
+        <v>4607894.2</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2009,28 +2024,28 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D44" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E44" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F44" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I44" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J44">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="K44">
-        <v>663.89</v>
+        <v>229850.62</v>
       </c>
       <c r="L44">
-        <v>39833.4</v>
+        <v>1838804.96</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2041,28 +2056,28 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="D45" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E45" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F45" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="I45" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J45">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="K45">
-        <v>209975.56</v>
+        <v>663.89</v>
       </c>
       <c r="L45">
-        <v>209975.56</v>
+        <v>39833.4</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2073,28 +2088,28 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D46" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E46" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F46" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="I46" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J46">
         <v>1</v>
       </c>
       <c r="K46">
-        <v>163002.7</v>
+        <v>12173.17</v>
       </c>
       <c r="L46">
-        <v>163002.7</v>
+        <v>12173.17</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2105,28 +2120,28 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D47" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E47" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F47" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="I47" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J47">
         <v>1</v>
       </c>
       <c r="K47">
-        <v>15384.67</v>
+        <v>163002.7</v>
       </c>
       <c r="L47">
-        <v>15384.67</v>
+        <v>163002.7</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2140,25 +2155,25 @@
         <v>73</v>
       </c>
       <c r="D48" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E48" t="s">
         <v>73</v>
       </c>
       <c r="F48" t="s">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="I48" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K48">
-        <v>193066.84</v>
+        <v>9156.48</v>
       </c>
       <c r="L48">
-        <v>386133.68</v>
+        <v>36625.92</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2169,28 +2184,28 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D49" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E49" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F49" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I49" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J49">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K49">
-        <v>26517.61</v>
+        <v>15384.67</v>
       </c>
       <c r="L49">
-        <v>132588.05</v>
+        <v>15384.67</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2201,27 +2216,91 @@
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D50" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E50" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="F50" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="I50" t="s">
+        <v>124</v>
+      </c>
+      <c r="J50">
+        <v>2</v>
+      </c>
+      <c r="K50">
+        <v>193066.84</v>
+      </c>
+      <c r="L50">
+        <v>386133.68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51" t="s">
+        <v>118</v>
+      </c>
+      <c r="E51" t="s">
+        <v>75</v>
+      </c>
+      <c r="F51" t="s">
+        <v>75</v>
+      </c>
+      <c r="I51" t="s">
+        <v>124</v>
+      </c>
+      <c r="J51">
+        <v>5</v>
+      </c>
+      <c r="K51">
+        <v>26517.61</v>
+      </c>
+      <c r="L51">
+        <v>132588.05</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52" t="s">
         <v>119</v>
       </c>
-      <c r="J50">
+      <c r="E52" t="s">
+        <v>121</v>
+      </c>
+      <c r="F52" t="s">
+        <v>121</v>
+      </c>
+      <c r="I52" t="s">
+        <v>124</v>
+      </c>
+      <c r="J52">
         <v>1</v>
       </c>
-      <c r="K50">
+      <c r="K52">
         <v>39099.54</v>
       </c>
-      <c r="L50">
+      <c r="L52">
         <v>39099.54</v>
       </c>
     </row>

--- a/Macro Inv Tarde/VALORIZADO FALTANTES IMPO.xlsx
+++ b/Macro Inv Tarde/VALORIZADO FALTANTES IMPO.xlsx
@@ -397,13 +397,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 30/11/2025 13:41:04</t>
+    <t>Período: 30/11/2025 13:21:00</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 05/11/2025 13:41:37</t>
+    <t>Fecha y hora de generación: 06/11/2025 13:21:33</t>
   </si>
 </sst>
 </file>
